--- a/.data/llm_additional_requirements.xlsx
+++ b/.data/llm_additional_requirements.xlsx
@@ -4416,7 +4416,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{FA6F8FD6-FF02-46F9-AB06-EC570D2533E5}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{0F7F7B59-312A-4AB5-AAFE-174B69C8D328}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:F392"/>
   <sheetFormatPr defaultRowHeight="14.399999999999999" defaultColWidth="9.140625" customHeight="1"/>
   <cols>
